--- a/data/EtoA_data.xlsx
+++ b/data/EtoA_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jackrosenbaum/artlight/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jackrosenbaum/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2628B395-89AE-4247-A765-A5C19EF642E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FF4477-3257-C44D-AE0F-8567B9B40E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1040" yWindow="1840" windowWidth="25700" windowHeight="16000" xr2:uid="{D7E03887-FC02-490D-B44C-E405D6284356}"/>
+    <workbookView xWindow="1640" yWindow="780" windowWidth="25700" windowHeight="16000" xr2:uid="{D7E03887-FC02-490D-B44C-E405D6284356}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="2" r:id="rId1"/>
@@ -7034,7 +7034,7 @@
     </row>
     <row r="62" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B62">
         <v>1</v>
@@ -7134,7 +7134,7 @@
     </row>
     <row r="63" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B63">
         <v>1</v>
@@ -7234,7 +7234,7 @@
     </row>
     <row r="64" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -7334,7 +7334,7 @@
     </row>
     <row r="65" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -7434,7 +7434,7 @@
     </row>
     <row r="66" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -7534,7 +7534,7 @@
     </row>
     <row r="67" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B67">
         <v>2</v>
@@ -7634,7 +7634,7 @@
     </row>
     <row r="68" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B68">
         <v>2</v>
@@ -7734,7 +7734,7 @@
     </row>
     <row r="69" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B69">
         <v>2</v>
@@ -7834,7 +7834,7 @@
     </row>
     <row r="70" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B70">
         <v>2</v>
@@ -7934,7 +7934,7 @@
     </row>
     <row r="71" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B71">
         <v>2</v>
@@ -8034,7 +8034,7 @@
     </row>
     <row r="72" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B72">
         <v>3</v>
@@ -8134,7 +8134,7 @@
     </row>
     <row r="73" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B73">
         <v>3</v>
@@ -8234,7 +8234,7 @@
     </row>
     <row r="74" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B74">
         <v>3</v>
@@ -8334,7 +8334,7 @@
     </row>
     <row r="75" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B75">
         <v>3</v>
@@ -8434,7 +8434,7 @@
     </row>
     <row r="76" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B76">
         <v>3</v>
@@ -8534,7 +8534,7 @@
     </row>
     <row r="77" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B77">
         <v>4</v>
@@ -8634,7 +8634,7 @@
     </row>
     <row r="78" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B78">
         <v>4</v>
@@ -8734,7 +8734,7 @@
     </row>
     <row r="79" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B79">
         <v>4</v>
@@ -8834,7 +8834,7 @@
     </row>
     <row r="80" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B80">
         <v>4</v>
@@ -8934,7 +8934,7 @@
     </row>
     <row r="81" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B81">
         <v>4</v>

--- a/data/EtoA_data.xlsx
+++ b/data/EtoA_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jackrosenbaum/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kigha\Documents\00phdyr1\artlight_bio708\artlight\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FF4477-3257-C44D-AE0F-8567B9B40E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1640" yWindow="780" windowWidth="25700" windowHeight="16000" xr2:uid="{D7E03887-FC02-490D-B44C-E405D6284356}"/>
+    <workbookView xWindow="2420" yWindow="2520" windowWidth="19200" windowHeight="11170" xr2:uid="{D7E03887-FC02-490D-B44C-E405D6284356}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="2" r:id="rId1"/>
@@ -594,21 +594,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5464EB31-8F43-4A0C-9DD7-C88BB7C084C7}">
   <dimension ref="A1:AH81"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.6640625" customWidth="1"/>
-    <col min="3" max="3" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="31" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="9.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.6328125" customWidth="1"/>
+    <col min="3" max="3" width="4.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="31" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.1796875" style="3" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="10" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="9.83203125" customWidth="1"/>
+    <col min="34" max="34" width="9.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -712,7 +712,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -820,7 +820,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -928,7 +928,7 @@
         <v>0.52380952380952384</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>0.63636363636363635</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1252,7 +1252,7 @@
         <v>0.6428571428571429</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>0.38095238095238093</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>0.5625</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1576,7 +1576,7 @@
         <v>0.29411764705882354</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>0.54545454545454541</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -2008,7 +2008,7 @@
         <v>0.53846153846153844</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -2116,7 +2116,7 @@
         <v>0.77777777777777779</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -2224,7 +2224,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -2440,7 +2440,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>0.47619047619047616</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -2656,7 +2656,7 @@
         <v>0.57894736842105265</v>
       </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>0.42105263157894735</v>
       </c>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -3088,7 +3088,7 @@
         <v>0.68421052631578949</v>
       </c>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -3196,7 +3196,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -3304,7 +3304,7 @@
         <v>0.52380952380952384</v>
       </c>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>0.57894736842105265</v>
       </c>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>9</v>
       </c>
@@ -3736,7 +3736,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>9</v>
       </c>
@@ -3844,7 +3844,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -3952,7 +3952,7 @@
         <v>0.58823529411764708</v>
       </c>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -4060,7 +4060,7 @@
         <v>0.52380952380952384</v>
       </c>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>9</v>
       </c>
@@ -4168,7 +4168,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -4276,7 +4276,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>9</v>
       </c>
@@ -4384,7 +4384,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -4492,7 +4492,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>9</v>
       </c>
@@ -4708,7 +4708,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>9</v>
       </c>
@@ -4816,7 +4816,7 @@
         <v>0.47619047619047616</v>
       </c>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>9</v>
       </c>
@@ -4924,7 +4924,7 @@
         <v>0.42857142857142855</v>
       </c>
     </row>
-    <row r="41" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>9</v>
       </c>
@@ -5032,7 +5032,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>8</v>
       </c>
@@ -5132,7 +5132,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>8</v>
       </c>
@@ -5232,7 +5232,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>8</v>
       </c>
@@ -5332,7 +5332,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>8</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>8</v>
       </c>
@@ -5532,7 +5532,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>8</v>
       </c>
@@ -5632,7 +5632,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>8</v>
       </c>
@@ -5732,7 +5732,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -5832,7 +5832,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>8</v>
       </c>
@@ -5932,7 +5932,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>8</v>
       </c>
@@ -6032,7 +6032,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>8</v>
       </c>
@@ -6132,7 +6132,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>8</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>8</v>
       </c>
@@ -6332,7 +6332,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>8</v>
       </c>
@@ -6432,7 +6432,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>8</v>
       </c>
@@ -6532,7 +6532,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>8</v>
       </c>
@@ -6632,7 +6632,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>8</v>
       </c>
@@ -6732,7 +6732,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>8</v>
       </c>
@@ -6832,7 +6832,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>8</v>
       </c>
@@ -6932,7 +6932,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>8</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>9</v>
       </c>
@@ -7132,7 +7132,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>9</v>
       </c>
@@ -7232,7 +7232,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>9</v>
       </c>
@@ -7332,7 +7332,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>9</v>
       </c>
@@ -7432,7 +7432,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>9</v>
       </c>
@@ -7532,7 +7532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>9</v>
       </c>
@@ -7632,7 +7632,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>9</v>
       </c>
@@ -7732,7 +7732,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>9</v>
       </c>
@@ -7832,7 +7832,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>9</v>
       </c>
@@ -7932,7 +7932,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>9</v>
       </c>
@@ -8032,7 +8032,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>9</v>
       </c>
@@ -8132,7 +8132,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>9</v>
       </c>
@@ -8232,7 +8232,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>9</v>
       </c>
@@ -8332,7 +8332,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>9</v>
       </c>
@@ -8432,7 +8432,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>9</v>
       </c>
@@ -8532,7 +8532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>9</v>
       </c>
@@ -8632,7 +8632,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>9</v>
       </c>
@@ -8732,7 +8732,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="79" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>9</v>
       </c>
@@ -8832,7 +8832,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="80" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>9</v>
       </c>
@@ -8932,7 +8932,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>9</v>
       </c>
